--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (68 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (71 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1254 +494,1320 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
+          <t>seg.groupsecurity@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>82752</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>PROC-15553</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>nmpb.tenders@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>80064</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>vt.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>uktnp.procurement@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Director of National Parks</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>14246</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (71 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (75 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,17 +494,17 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>tenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>PROC-9177424</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -516,17 +516,17 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+          <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PROC-15553</t>
+          <t>FSANZ-2026/6</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -536,22 +536,22 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>nmpb.tenders@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>seg.groupsecurity@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>80064</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>82752</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -560,87 +560,95 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Australian Taxation Office</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PROC-15553</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>territories_projects@infrastructure.gov.au</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>10032193</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>est10003@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DCET2026-01A</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>tenders@hsra.gov.au</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>High Speed Rail Authority</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>10031970</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>brtenders@grdc.com.au</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Grains Research and Development Corporation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Proc-9177441</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>tenders@ga.gov.au</t>
+          <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
       <c r="B9" s="3" t="n"/>
@@ -654,17 +662,17 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>tenders@finance.gov.au</t>
+          <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A Testing Agency</t>
+          <t>Director of National Parks</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>DemoATM2026</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,17 +684,17 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>tenders@dha.gov.au</t>
+          <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Defence Housing Australia</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>DHAPROC26/750</t>
+          <t>10032193</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -698,11 +706,19 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+          <t>tenders@hsra.gov.au</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>High Speed Rail Authority</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>10031970</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -712,19 +728,11 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>tenders@aims.gov.au</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Australian Institute of Marine Science</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>AIMSRFT785</t>
-        </is>
-      </c>
+          <t>tenders@ga.gov.au</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -734,11 +742,19 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>tender-pwles@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+          <t>tenders@finance.gov.au</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>A Testing Agency</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>DemoATM2026</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -748,17 +764,17 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>statssection@dfat.gov.au</t>
+          <t>tenders@dha.gov.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Defence Housing Australia</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>DFAT - 26/7254-10</t>
+          <t>DHAPROC26/750</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -770,7 +786,7 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ss.finance@dcceew.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
@@ -784,11 +800,19 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+          <t>tenders@aims.gov.au</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Australian Institute of Marine Science</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>AIMSRFT785</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -798,19 +822,11 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>spacecyber.events@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>JCGSCIF26-3</t>
-        </is>
-      </c>
+          <t>tender-pwles@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -820,17 +836,17 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>snsw.pds.tenders@aurecongroup.com</t>
+          <t>statssection@dfat.gov.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>S-EST11298</t>
+          <t>DFAT - 26/7254-10</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -842,7 +858,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
+          <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
@@ -856,7 +872,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>smptenders@dta.gov.au</t>
+          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
       <c r="B21" s="3" t="n"/>
@@ -870,7 +886,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>segservicedelivery.esddewpo@defence.gov.au</t>
+          <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -880,7 +896,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>EWPNOTICE 01/2026</t>
+          <t>JCGSCIF26-3</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -892,11 +908,19 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>rfi15434@ato.gov.au</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+          <t>snsw.pds.tenders@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>S-EST11298</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -906,19 +930,11 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>resp.priv.hospitals@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>PHS-16</t>
-        </is>
-      </c>
+          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -928,7 +944,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>raiprocurement@infrastructure.gov.au</t>
+          <t>smptenders@dta.gov.au</t>
         </is>
       </c>
       <c r="B25" s="3" t="n"/>
@@ -942,11 +958,19 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>qld.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+          <t>segservicedelivery.esddewpo@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>EWPNOTICE 01/2026</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -956,19 +980,11 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>psprocurement@nca.gov.au</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>National Capital Authority</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>A26/11/1</t>
-        </is>
-      </c>
+          <t>rfi15434@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -978,11 +994,19 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>procurement@rba.gov.au</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+          <t>resp.priv.hospitals@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PHS-16</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -992,7 +1016,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>procurement@npg.gov.au</t>
+          <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
@@ -1006,7 +1030,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>procurement@moadoph.gov.au</t>
+          <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
@@ -1020,17 +1044,17 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>procurement@harbourtrust.gov.au</t>
+          <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Sydney Harbour Federation Trust</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>SHFT26015</t>
+          <t>A26/11/1</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1042,19 +1066,11 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>procurement@aciar.gov.au</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Australian Centre for International Agricultural Research</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>C005676</t>
-        </is>
-      </c>
+          <t>procurement@rba.gov.au</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1064,19 +1080,11 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>procurement.cop31@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>PPCOP31T-26</t>
-        </is>
-      </c>
+          <t>procurement@npg.gov.au</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1086,19 +1094,11 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>phwp.mtr@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>25A143</t>
-        </is>
-      </c>
+          <t>procurement@moadoph.gov.au</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1108,11 +1108,19 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>pdsvictas@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
+          <t>procurement@harbourtrust.gov.au</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Sydney Harbour Federation Trust</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>SHFT26015</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1122,11 +1130,19 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>pdssa@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+          <t>procurement@aciar.gov.au</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Australian Centre for International Agricultural Research</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>C005676</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1136,17 +1152,17 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>pds.vic.tenders@mottmac.com</t>
+          <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>S-EST10700</t>
+          <t>PPCOP31T-26</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1158,17 +1174,17 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>pds.sa.tenders@mottmac.com</t>
+          <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>S-EST10707</t>
+          <t>25A143</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1180,19 +1196,11 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>nbscdtender@health.gov.au</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Department of Health, Disability and Ageing</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Health/E25-515102</t>
-        </is>
-      </c>
+          <t>pdsvictas@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1202,19 +1210,11 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>mscspo.vlfrft@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>JSD/RFT/75462/1</t>
-        </is>
-      </c>
+          <t>pdssa@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1224,17 +1224,17 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>mgf.contracts@dva.gov.au</t>
+          <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>MGF_17</t>
+          <t>S-EST10700</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1246,11 +1246,19 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>maugeanskateprogam@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
+          <t>pds.sa.tenders@mottmac.com</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>S-EST10707</t>
+        </is>
+      </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1260,17 +1268,17 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>knowlert@ansto.gov.au</t>
+          <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Australian Nuclear Science and Technology Organisation</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PSC002829</t>
+          <t>Health/E25-515102</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1282,17 +1290,17 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ippreform@niaa.gov.au</t>
+          <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PROC0018432 - NOTICE</t>
+          <t>JSD/RFT/75462/1</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1304,11 +1312,19 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ipinfra.west@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
+          <t>mgf.contracts@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MGF_17</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1318,19 +1334,11 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ests4000ph6@rpsconsulting.com</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>AZ6622</t>
-        </is>
-      </c>
+          <t>maugeanskateprogam@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1340,11 +1348,19 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>entrylevelprograms@treasury.gov.au</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
+          <t>knowlert@ansto.gov.au</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Australian Nuclear Science and Technology Organisation</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PSC002829</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1354,17 +1370,17 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>emily.costello@ramint.gov.au</t>
+          <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Royal Australian Mint</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F26860-2</t>
+          <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -1376,19 +1392,11 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>drisl@resources.defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>AZ6621</t>
-        </is>
-      </c>
+          <t>ipinfra.west@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1398,17 +1406,17 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>dpc.invitation@dva.gov.au</t>
+          <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>DPC-2017</t>
+          <t>AZ6622</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -1420,7 +1428,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>defence.newsmarketing@defence.gov.au</t>
+          <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="n"/>
@@ -1434,17 +1442,17 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>def08101.acquisitions@defence.gov.au</t>
+          <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Royal Australian Mint</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFI/88220/1</t>
+          <t>F26860-2</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -1456,11 +1464,19 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>decomdirectorate@industry.gov.au</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
+          <t>drisl@resources.defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>AZ6621</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1470,11 +1486,19 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>csiroeoi2026008@csiro.au</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
+          <t>dpc.invitation@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>DPC-2017</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1484,7 +1508,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
+          <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
       <c r="B55" s="3" t="n"/>
@@ -1498,11 +1522,19 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>contracts@aad.gov.au</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
+          <t>def08101.acquisitions@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFI/88220/1</t>
+        </is>
+      </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1512,7 +1544,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>contracts-enquiries@amsa.gov.au</t>
+          <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
       <c r="B57" s="3" t="n"/>
@@ -1526,7 +1558,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>commercialprojects@niaa.gov.au</t>
+          <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
       <c r="B58" s="3" t="n"/>
@@ -1540,19 +1572,11 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>cn.agreement@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>CNS16</t>
-        </is>
-      </c>
+          <t>cop31procurement@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
       <c r="D59" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1562,19 +1586,11 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>cfi.trainingandevents@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>CFI-20260825</t>
-        </is>
-      </c>
+          <t>contracts@aad.gov.au</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1584,7 +1600,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>cei.policy@dcceew.gov.au</t>
+          <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
       <c r="B61" s="3" t="n"/>
@@ -1598,19 +1614,11 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>LSD/RFP/54755/1</t>
-        </is>
-      </c>
+          <t>commercialprojects@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
       <c r="D62" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1620,17 +1628,17 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>bianca.james@nma.gov.au</t>
+          <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>National Museum of Australia</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>NMAT2526/14</t>
+          <t>CNS16</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -1642,11 +1650,19 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>asqapanel@asqa.gov.au</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
+          <t>cfi.trainingandevents@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>CFI-20260825</t>
+        </is>
+      </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1656,7 +1672,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>asca.innovationchallenges@defence.gov.au</t>
+          <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B65" s="3" t="n"/>
@@ -1670,17 +1686,17 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>army.industry@defence.gov.au</t>
+          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>LCD LEWG 2026</t>
+          <t>LSD/RFP/54755/1</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -1692,11 +1708,19 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>alireza.taghipour@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
+          <t>bianca.james@nma.gov.au</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>National Museum of Australia</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>NMAT2526/14</t>
+        </is>
+      </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1706,19 +1730,11 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>alexandra.torney@humanrights.gov.au</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Australian Human Rights Commission</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>National Youth OYT</t>
-        </is>
-      </c>
+          <t>asqapanel@asqa.gov.au</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
       <c r="D68" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1728,19 +1744,11 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>afp-rft@afp.gov.au</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Australian Federal Police</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>REOI 06-2026</t>
-        </is>
-      </c>
+          <t>asca.innovationchallenges@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1750,17 +1758,17 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>aegis.training@defence.gov.au</t>
+          <t>army.industry@defence.gov.au</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>MSCCS/RFT/77626/1</t>
+          <t>LCD LEWG 2026</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -1772,19 +1780,11 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>adffhp.procurement@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>ADFFHP IndustryNotic</t>
-        </is>
-      </c>
+          <t>alireza.taghipour@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1794,20 +1794,108 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
+          <t>alexandra.torney@humanrights.gov.au</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Australian Human Rights Commission</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>National Youth OYT</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>afp-rft@afp.gov.au</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Australian Federal Police</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>REOI 06-2026</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>aegis.training@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>MSCCS/RFT/77626/1</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>adffhp.procurement@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>ADFFHP IndustryNotic</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,66 +524,66 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -646,1256 +634,1256 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (75 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (79 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1408 +494,1496 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tenders@grdc.com.au</t>
+          <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PROC-9177424</t>
+          <t>ESE24/1125-B</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tenders@foodstandards.gov.au</t>
+          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Food Standards Australia New Zealand</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>FSANZ-2026/6</t>
+          <t>Kingscote EOI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>JSD/RFT/76225/1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>capitalprojects@questacon.edu.au</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Department of Industry, Science and Resources</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ATM_2026_3289</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>tenders@grdc.com.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Grains Research and Development Corporation</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>PROC-9177424</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>tenders@foodstandards.gov.au</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Food Standards Australia New Zealand</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>FSANZ-2026/6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>seg.groupsecurity@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>82752</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,1410 +568,1410 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>tenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>PROC-9177424</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>FSANZ-2026/6</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (79 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (80 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1496 +494,1518 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>rcmemorial@nca.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>National Capital Authority</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ATM26/14</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ESE24/1125-B</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Kingscote EOI</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/76225/1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>ATM_2026_3289</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>tenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>PROC-9177424</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>FSANZ-2026/6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -514,1498 +502,1498 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ESE24/1125-B</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Kingscote EOI</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/76225/1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>ATM_2026_3289</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>PROC-9177424</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>FSANZ-2026/6</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (80 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (81 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1518 +494,1540 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>protocol.branch@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DFAT-EXD-AFS01</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ATM26/14</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ESE24/1125-B</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Kingscote EOI</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/76225/1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>ATM_2026_3289</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>tenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>PROC-9177424</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>FSANZ-2026/6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (81 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (83 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,105 +494,105 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>protocol.branch@dfat.gov.au</t>
+          <t>saeoipreston.wdaus@jll.com</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DFAT-EXD-AFS01</t>
+          <t>EOI PRESTON VIC</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>rcmemorial@nca.gov.au</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>National Capital Authority</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ATM26/14</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>procurement@exportfinance.gov.au</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Export Finance Australia</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EFA2026002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>procurementandgrants@dewr.gov.au</t>
+          <t>protocol.branch@dfat.gov.au</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ESE24/1125-B</t>
+          <t>DFAT-EXD-AFS01</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
+          <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kingscote EOI</t>
+          <t>ATM26/14</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
+          <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/76225/1</t>
+          <t>ESE24/1125-B</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -604,17 +604,17 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>capitalprojects@questacon.edu.au</t>
+          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ATM_2026_3289</t>
+          <t>Kingscote EOI</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -626,61 +626,61 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>tenders@grdc.com.au</t>
+          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>PROC-9177424</t>
+          <t>JSD/RFT/76225/1</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>tenders@foodstandards.gov.au</t>
+          <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Food Standards Australia New Zealand</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FSANZ-2026/6</t>
+          <t>ATM_2026_3289</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>tenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>PROC-9177424</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -692,17 +692,17 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+          <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>PROC-15553</t>
+          <t>FSANZ-2026/6</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>nmpb.tenders@defence.gov.au</t>
+          <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>82752</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -736,17 +736,17 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>est10003@aurecongroup.com</t>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>DCET2026-01A</t>
+          <t>PROC-15553</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -758,17 +758,17 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>brtenders@grdc.com.au</t>
+          <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Proc-9177441</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -780,55 +780,55 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+          <t>est10003@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DCET2026-01A</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>brtenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>Proc-9177441</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>territories_projects@infrastructure.gov.au</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>10032193</t>
-        </is>
-      </c>
+          <t>vt.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -838,17 +838,17 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>tenders@hsra.gov.au</t>
+          <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>High Speed Rail Authority</t>
+          <t>Director of National Parks</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>10031970</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -860,11 +860,19 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>tenders@ga.gov.au</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
+          <t>territories_projects@infrastructure.gov.au</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>10032193</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -874,17 +882,17 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>tenders@finance.gov.au</t>
+          <t>tenders@hsra.gov.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>A Testing Agency</t>
+          <t>High Speed Rail Authority</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>DemoATM2026</t>
+          <t>10031970</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -896,19 +904,11 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>tenders@dha.gov.au</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Defence Housing Australia</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>DHAPROC26/750</t>
-        </is>
-      </c>
+          <t>tenders@ga.gov.au</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -918,11 +918,19 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+          <t>tenders@finance.gov.au</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>A Testing Agency</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>DemoATM2026</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -932,17 +940,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>tenders@aims.gov.au</t>
+          <t>tenders@dha.gov.au</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Australian Institute of Marine Science</t>
+          <t>Defence Housing Australia</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>AIMSRFT785</t>
+          <t>DHAPROC26/750</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -954,7 +962,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>tender-pwles@dfat.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B24" s="3" t="n"/>
@@ -968,17 +976,17 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>statssection@dfat.gov.au</t>
+          <t>tenders@aims.gov.au</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Australian Institute of Marine Science</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>DFAT - 26/7254-10</t>
+          <t>AIMSRFT785</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -990,7 +998,7 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ss.finance@dcceew.gov.au</t>
+          <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
@@ -1004,11 +1012,19 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+          <t>statssection@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>DFAT - 26/7254-10</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1018,19 +1034,11 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>spacecyber.events@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>JCGSCIF26-3</t>
-        </is>
-      </c>
+          <t>ss.finance@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1040,19 +1048,11 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>snsw.pds.tenders@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>S-EST11298</t>
-        </is>
-      </c>
+          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1062,11 +1062,19 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
+          <t>spacecyber.events@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>JCGSCIF26-3</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1076,11 +1084,19 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>smptenders@dta.gov.au</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
+          <t>snsw.pds.tenders@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>S-EST11298</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1090,19 +1106,11 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>segservicedelivery.esddewpo@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>EWPNOTICE 01/2026</t>
-        </is>
-      </c>
+          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1112,7 +1120,7 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>rfi15434@ato.gov.au</t>
+          <t>smptenders@dta.gov.au</t>
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
@@ -1126,17 +1134,17 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>resp.priv.hospitals@dva.gov.au</t>
+          <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>PHS-16</t>
+          <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1148,7 +1156,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>raiprocurement@infrastructure.gov.au</t>
+          <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
       <c r="B35" s="3" t="n"/>
@@ -1162,11 +1170,19 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>qld.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+          <t>resp.priv.hospitals@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>PHS-16</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1176,19 +1192,11 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>psprocurement@nca.gov.au</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>National Capital Authority</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>A26/11/1</t>
-        </is>
-      </c>
+          <t>raiprocurement@infrastructure.gov.au</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1198,7 +1206,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>procurement@rba.gov.au</t>
+          <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
       <c r="B38" s="3" t="n"/>
@@ -1212,11 +1220,19 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>procurement@npg.gov.au</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
+          <t>psprocurement@nca.gov.au</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>National Capital Authority</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>A26/11/1</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1226,7 +1242,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>procurement@moadoph.gov.au</t>
+          <t>procurement@rba.gov.au</t>
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
@@ -1240,19 +1256,11 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>procurement@harbourtrust.gov.au</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Sydney Harbour Federation Trust</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>SHFT26015</t>
-        </is>
-      </c>
+          <t>procurement@npg.gov.au</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1262,19 +1270,11 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>procurement@aciar.gov.au</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Australian Centre for International Agricultural Research</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>C005676</t>
-        </is>
-      </c>
+          <t>procurement@moadoph.gov.au</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1284,17 +1284,17 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>procurement.cop31@dfat.gov.au</t>
+          <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PPCOP31T-26</t>
+          <t>SHFT26015</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1306,17 +1306,17 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>phwp.mtr@dfat.gov.au</t>
+          <t>procurement@aciar.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
+          <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>25A143</t>
+          <t>C005676</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1328,11 +1328,19 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>pdsvictas@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
+          <t>procurement.cop31@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>PPCOP31T-26</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1342,11 +1350,19 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>pdssa@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
+          <t>phwp.mtr@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>25A143</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1356,19 +1372,11 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>pds.vic.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>S-EST10700</t>
-        </is>
-      </c>
+          <t>pdsvictas@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1378,19 +1386,11 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>pds.sa.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>S-EST10707</t>
-        </is>
-      </c>
+          <t>pdssa@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1400,17 +1400,17 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>nbscdtender@health.gov.au</t>
+          <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Health/E25-515102</t>
+          <t>S-EST10700</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -1422,17 +1422,17 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>mscspo.vlfrft@defence.gov.au</t>
+          <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/75462/1</t>
+          <t>S-EST10707</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -1444,17 +1444,17 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>mgf.contracts@dva.gov.au</t>
+          <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>MGF_17</t>
+          <t>Health/E25-515102</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -1466,11 +1466,19 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>maugeanskateprogam@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
+          <t>mscspo.vlfrft@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFT/75462/1</t>
+        </is>
+      </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1480,17 +1488,17 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>knowlert@ansto.gov.au</t>
+          <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Australian Nuclear Science and Technology Organisation</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>PSC002829</t>
+          <t>MGF_17</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -1502,19 +1510,11 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ippreform@niaa.gov.au</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>National Indigenous Australians Agency</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>PROC0018432 - NOTICE</t>
-        </is>
-      </c>
+          <t>maugeanskateprogam@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
       <c r="D54" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1524,11 +1524,19 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ipinfra.west@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
+          <t>knowlert@ansto.gov.au</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Australian Nuclear Science and Technology Organisation</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>PSC002829</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1538,17 +1546,17 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ests4000ph6@rpsconsulting.com</t>
+          <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>AZ6622</t>
+          <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -1560,7 +1568,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>entrylevelprograms@treasury.gov.au</t>
+          <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
       <c r="B57" s="3" t="n"/>
@@ -1574,17 +1582,17 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>emily.costello@ramint.gov.au</t>
+          <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Royal Australian Mint</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>F26860-2</t>
+          <t>AZ6622</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1596,19 +1604,11 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>drisl@resources.defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>AZ6621</t>
-        </is>
-      </c>
+          <t>entrylevelprograms@treasury.gov.au</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
       <c r="D59" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1618,17 +1618,17 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>dpc.invitation@dva.gov.au</t>
+          <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Royal Australian Mint</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>DPC-2017</t>
+          <t>F26860-2</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1640,11 +1640,19 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>defence.newsmarketing@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
+          <t>drisl@resources.defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>AZ6621</t>
+        </is>
+      </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1654,17 +1662,17 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>def08101.acquisitions@defence.gov.au</t>
+          <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFI/88220/1</t>
+          <t>DPC-2017</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -1676,7 +1684,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>decomdirectorate@industry.gov.au</t>
+          <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
       <c r="B63" s="3" t="n"/>
@@ -1690,11 +1698,19 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>csiroeoi2026008@csiro.au</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
+          <t>def08101.acquisitions@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFI/88220/1</t>
+        </is>
+      </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1704,7 +1720,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
+          <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
       <c r="B65" s="3" t="n"/>
@@ -1718,7 +1734,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>contracts@aad.gov.au</t>
+          <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
       <c r="B66" s="3" t="n"/>
@@ -1732,7 +1748,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>contracts-enquiries@amsa.gov.au</t>
+          <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B67" s="3" t="n"/>
@@ -1746,7 +1762,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>commercialprojects@niaa.gov.au</t>
+          <t>contracts@aad.gov.au</t>
         </is>
       </c>
       <c r="B68" s="3" t="n"/>
@@ -1760,19 +1776,11 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>cn.agreement@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>CNS16</t>
-        </is>
-      </c>
+          <t>contracts-enquiries@amsa.gov.au</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1782,19 +1790,11 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>cfi.trainingandevents@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>CFI-20260825</t>
-        </is>
-      </c>
+          <t>commercialprojects@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
       <c r="D70" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1804,11 +1804,19 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>cei.policy@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
+          <t>cn.agreement@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>CNS16</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1818,17 +1826,17 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+          <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>LSD/RFP/54755/1</t>
+          <t>CFI-20260825</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -1840,19 +1848,11 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>bianca.james@nma.gov.au</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>National Museum of Australia</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>NMAT2526/14</t>
-        </is>
-      </c>
+          <t>cei.policy@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1862,11 +1862,19 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>asqapanel@asqa.gov.au</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
+          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>LSD/RFP/54755/1</t>
+        </is>
+      </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1876,11 +1884,19 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>asca.innovationchallenges@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
+          <t>bianca.james@nma.gov.au</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>National Museum of Australia</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>NMAT2526/14</t>
+        </is>
+      </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1890,19 +1906,11 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>army.industry@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>LCD LEWG 2026</t>
-        </is>
-      </c>
+          <t>asqapanel@asqa.gov.au</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
       <c r="D76" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1912,7 +1920,7 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>alireza.taghipour@dcceew.gov.au</t>
+          <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
       <c r="B77" s="3" t="n"/>
@@ -1926,17 +1934,17 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>alexandra.torney@humanrights.gov.au</t>
+          <t>army.industry@defence.gov.au</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Australian Human Rights Commission</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>National Youth OYT</t>
+          <t>LCD LEWG 2026</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -1948,19 +1956,11 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>afp-rft@afp.gov.au</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Australian Federal Police</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>REOI 06-2026</t>
-        </is>
-      </c>
+          <t>alireza.taghipour@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1970,17 +1970,17 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>aegis.training@defence.gov.au</t>
+          <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Australian Human Rights Commission</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>MSCCS/RFT/77626/1</t>
+          <t>National Youth OYT</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -1992,17 +1992,17 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>adffhp.procurement@defence.gov.au</t>
+          <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Federal Police</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>ADFFHP IndustryNotic</t>
+          <t>REOI 06-2026</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -2014,20 +2014,64 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
+          <t>aegis.training@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>MSCCS/RFT/77626/1</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>adffhp.procurement@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>ADFFHP IndustryNotic</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (83 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (88 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,117 +494,117 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>saeoipreston.wdaus@jll.com</t>
+          <t>tenders@opc.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EOI PRESTON VIC</t>
+          <t>OPC- 2026-02</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>stephanie.scroope@moadoph.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Export Finance Australia</t>
+          <t>Old Parliament House</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EFA2026002</t>
+          <t>MoAD-ATM-7493</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>protocol.branch@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>DFAT-EXD-AFS01</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>qldtenders.pds@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>S-EST11096</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>rcmemorial@nca.gov.au</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>National Capital Authority</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ATM26/14</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>pds.wa.tenders@mottmac.com</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>S-EST10796</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>procurementandgrants@dewr.gov.au</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Department of Employment and Workplace Relations</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ESE24/1125-B</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>drisl.cfi@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>AZ6621</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
+          <t>saeoipreston.wdaus@jll.com</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -614,183 +614,183 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Kingscote EOI</t>
+          <t>EOI PRESTON VIC</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
+          <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Export Finance Australia</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/76225/1</t>
+          <t>EFA2026002</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>capitalprojects@questacon.edu.au</t>
+          <t>protocol.branch@dfat.gov.au</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ATM_2026_3289</t>
+          <t>DFAT-EXD-AFS01</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>tenders@grdc.com.au</t>
+          <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>PROC-9177424</t>
+          <t>ATM26/14</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>tenders@foodstandards.gov.au</t>
+          <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Food Standards Australia New Zealand</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FSANZ-2026/6</t>
+          <t>ESE24/1125-B</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>Kingscote EOI</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PROC-15553</t>
+          <t>JSD/RFT/76225/1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>nmpb.tenders@defence.gov.au</t>
+          <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>ATM_2026_3289</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>est10003@aurecongroup.com</t>
+          <t>tenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>DCET2026-01A</t>
+          <t>PROC-9177424</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -802,17 +802,17 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>brtenders@grdc.com.au</t>
+          <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Proc-9177441</t>
+          <t>FSANZ-2026/6</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -824,113 +824,121 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+          <t>seg.groupsecurity@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>82752</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>PROC-15553</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>territories_projects@infrastructure.gov.au</t>
+          <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>10032193</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>tenders@hsra.gov.au</t>
+          <t>est10003@aurecongroup.com</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>High Speed Rail Authority</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>10031970</t>
+          <t>DCET2026-01A</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>tenders@ga.gov.au</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
+          <t>brtenders@grdc.com.au</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Grains Research and Development Corporation</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Proc-9177441</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>tenders@finance.gov.au</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>A Testing Agency</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>DemoATM2026</t>
-        </is>
-      </c>
+          <t>vt.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -940,17 +948,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>tenders@dha.gov.au</t>
+          <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Defence Housing Australia</t>
+          <t>Director of National Parks</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>DHAPROC26/750</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -962,11 +970,19 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
+          <t>territories_projects@infrastructure.gov.au</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>10032193</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -976,17 +992,17 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>tenders@aims.gov.au</t>
+          <t>tenders@hsra.gov.au</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Australian Institute of Marine Science</t>
+          <t>High Speed Rail Authority</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>AIMSRFT785</t>
+          <t>10031970</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -998,7 +1014,7 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>tender-pwles@dfat.gov.au</t>
+          <t>tenders@ga.gov.au</t>
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
@@ -1012,17 +1028,17 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>statssection@dfat.gov.au</t>
+          <t>tenders@finance.gov.au</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>A Testing Agency</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>DFAT - 26/7254-10</t>
+          <t>DemoATM2026</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1034,11 +1050,19 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ss.finance@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+          <t>tenders@dha.gov.au</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Defence Housing Australia</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>DHAPROC26/750</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1048,7 +1072,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
@@ -1062,17 +1086,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>spacecyber.events@defence.gov.au</t>
+          <t>tenders@aims.gov.au</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Institute of Marine Science</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>JCGSCIF26-3</t>
+          <t>AIMSRFT785</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1084,19 +1108,11 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>snsw.pds.tenders@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>S-EST11298</t>
-        </is>
-      </c>
+          <t>tender-pwles@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1106,11 +1122,19 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
+          <t>statssection@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>DFAT - 26/7254-10</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1120,7 +1144,7 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>smptenders@dta.gov.au</t>
+          <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B33" s="3" t="n"/>
@@ -1134,19 +1158,11 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>segservicedelivery.esddewpo@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>EWPNOTICE 01/2026</t>
-        </is>
-      </c>
+          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1156,11 +1172,19 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>rfi15434@ato.gov.au</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
+          <t>spacecyber.events@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>JCGSCIF26-3</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1170,17 +1194,17 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>resp.priv.hospitals@dva.gov.au</t>
+          <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>PHS-16</t>
+          <t>S-EST11298</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1192,7 +1216,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>raiprocurement@infrastructure.gov.au</t>
+          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
       <c r="B37" s="3" t="n"/>
@@ -1206,7 +1230,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>qld.pds@bureauveritas.com</t>
+          <t>smptenders@dta.gov.au</t>
         </is>
       </c>
       <c r="B38" s="3" t="n"/>
@@ -1220,17 +1244,17 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>psprocurement@nca.gov.au</t>
+          <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>National Capital Authority</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>A26/11/1</t>
+          <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1242,7 +1266,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>procurement@rba.gov.au</t>
+          <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
@@ -1256,11 +1280,19 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>procurement@npg.gov.au</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
+          <t>resp.priv.hospitals@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PHS-16</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1270,7 +1302,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>procurement@moadoph.gov.au</t>
+          <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B42" s="3" t="n"/>
@@ -1284,19 +1316,11 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>procurement@harbourtrust.gov.au</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Sydney Harbour Federation Trust</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>SHFT26015</t>
-        </is>
-      </c>
+          <t>qld.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1306,17 +1330,17 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>procurement@aciar.gov.au</t>
+          <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Australian Centre for International Agricultural Research</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>C005676</t>
+          <t>A26/11/1</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1328,19 +1352,11 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>procurement.cop31@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>PPCOP31T-26</t>
-        </is>
-      </c>
+          <t>procurement@rba.gov.au</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1350,19 +1366,11 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>phwp.mtr@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>25A143</t>
-        </is>
-      </c>
+          <t>procurement@npg.gov.au</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1372,7 +1380,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>pdsvictas@aurecongroup.com</t>
+          <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
       <c r="B47" s="3" t="n"/>
@@ -1386,11 +1394,19 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>pdssa@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+          <t>procurement@harbourtrust.gov.au</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Sydney Harbour Federation Trust</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>SHFT26015</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1400,17 +1416,17 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>pds.vic.tenders@mottmac.com</t>
+          <t>procurement@aciar.gov.au</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>S-EST10700</t>
+          <t>C005676</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -1422,17 +1438,17 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>pds.sa.tenders@mottmac.com</t>
+          <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>S-EST10707</t>
+          <t>PPCOP31T-26</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -1444,17 +1460,17 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>nbscdtender@health.gov.au</t>
+          <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Health/E25-515102</t>
+          <t>25A143</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -1466,19 +1482,11 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>mscspo.vlfrft@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>JSD/RFT/75462/1</t>
-        </is>
-      </c>
+          <t>pdsvictas@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1488,19 +1496,11 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>mgf.contracts@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>MGF_17</t>
-        </is>
-      </c>
+          <t>pdssa@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
       <c r="D53" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1510,11 +1510,19 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>maugeanskateprogam@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
+          <t>pds.vic.tenders@mottmac.com</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>S-EST10700</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1524,17 +1532,17 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>knowlert@ansto.gov.au</t>
+          <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Australian Nuclear Science and Technology Organisation</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>PSC002829</t>
+          <t>S-EST10707</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -1546,17 +1554,17 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ippreform@niaa.gov.au</t>
+          <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>PROC0018432 - NOTICE</t>
+          <t>Health/E25-515102</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -1568,11 +1576,19 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ipinfra.west@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
+          <t>mscspo.vlfrft@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFT/75462/1</t>
+        </is>
+      </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1582,17 +1598,17 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ests4000ph6@rpsconsulting.com</t>
+          <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>AZ6622</t>
+          <t>MGF_17</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1604,7 +1620,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>entrylevelprograms@treasury.gov.au</t>
+          <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B59" s="3" t="n"/>
@@ -1618,17 +1634,17 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>emily.costello@ramint.gov.au</t>
+          <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Royal Australian Mint</t>
+          <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>F26860-2</t>
+          <t>PSC002829</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1640,17 +1656,17 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>drisl@resources.defence.gov.au</t>
+          <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>AZ6621</t>
+          <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -1662,19 +1678,11 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>dpc.invitation@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>DPC-2017</t>
-        </is>
-      </c>
+          <t>ipinfra.west@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
       <c r="D62" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1684,11 +1692,19 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>defence.newsmarketing@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
+          <t>ests4000ph6@rpsconsulting.com</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>AZ6622</t>
+        </is>
+      </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1698,19 +1714,11 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>def08101.acquisitions@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>JSD/RFI/88220/1</t>
-        </is>
-      </c>
+          <t>entrylevelprograms@treasury.gov.au</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1720,11 +1728,19 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>decomdirectorate@industry.gov.au</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
+          <t>emily.costello@ramint.gov.au</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Royal Australian Mint</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>F26860-2</t>
+        </is>
+      </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1734,11 +1750,19 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>csiroeoi2026008@csiro.au</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
+          <t>drisl@resources.defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>AZ6621</t>
+        </is>
+      </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1748,11 +1772,19 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
+          <t>dpc.invitation@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>DPC-2017</t>
+        </is>
+      </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1762,7 +1794,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>contracts@aad.gov.au</t>
+          <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
       <c r="B68" s="3" t="n"/>
@@ -1776,11 +1808,19 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>contracts-enquiries@amsa.gov.au</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
+          <t>def08101.acquisitions@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFI/88220/1</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1790,7 +1830,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>commercialprojects@niaa.gov.au</t>
+          <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
       <c r="B70" s="3" t="n"/>
@@ -1804,19 +1844,11 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>cn.agreement@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>CNS16</t>
-        </is>
-      </c>
+          <t>csiroeoi2026008@csiro.au</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1826,19 +1858,11 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>cfi.trainingandevents@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>CFI-20260825</t>
-        </is>
-      </c>
+          <t>cop31procurement@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
       <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1848,7 +1872,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>cei.policy@dcceew.gov.au</t>
+          <t>contracts@aad.gov.au</t>
         </is>
       </c>
       <c r="B73" s="3" t="n"/>
@@ -1862,19 +1886,11 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>LSD/RFP/54755/1</t>
-        </is>
-      </c>
+          <t>contracts-enquiries@amsa.gov.au</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
       <c r="D74" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1884,19 +1900,11 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>bianca.james@nma.gov.au</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>National Museum of Australia</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>NMAT2526/14</t>
-        </is>
-      </c>
+          <t>commercialprojects@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
       <c r="D75" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1906,11 +1914,19 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>asqapanel@asqa.gov.au</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
+          <t>cn.agreement@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>CNS16</t>
+        </is>
+      </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1920,11 +1936,19 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>asca.innovationchallenges@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
+          <t>cfi.trainingandevents@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>CFI-20260825</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1934,19 +1958,11 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>army.industry@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>LCD LEWG 2026</t>
-        </is>
-      </c>
+          <t>cei.policy@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
       <c r="D78" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1956,11 +1972,19 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>alireza.taghipour@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
+          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>LSD/RFP/54755/1</t>
+        </is>
+      </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1970,17 +1994,17 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>alexandra.torney@humanrights.gov.au</t>
+          <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Australian Human Rights Commission</t>
+          <t>National Museum of Australia</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>National Youth OYT</t>
+          <t>NMAT2526/14</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -1992,19 +2016,11 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>afp-rft@afp.gov.au</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Australian Federal Police</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>REOI 06-2026</t>
-        </is>
-      </c>
+          <t>asqapanel@asqa.gov.au</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
       <c r="D81" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2014,19 +2030,11 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>aegis.training@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>MSCCS/RFT/77626/1</t>
-        </is>
-      </c>
+          <t>asca.innovationchallenges@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2036,7 +2044,7 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>adffhp.procurement@defence.gov.au</t>
+          <t>army.industry@defence.gov.au</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2046,7 +2054,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>ADFFHP IndustryNotic</t>
+          <t>LCD LEWG 2026</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -2058,20 +2066,122 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
+          <t>alireza.taghipour@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>alexandra.torney@humanrights.gov.au</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Australian Human Rights Commission</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>National Youth OYT</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>afp-rft@afp.gov.au</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Australian Federal Police</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>REOI 06-2026</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>aegis.training@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>MSCCS/RFT/77626/1</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>adffhp.procurement@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>ADFFHP IndustryNotic</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (88 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (91 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,108 +494,108 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tenders@opc.gov.au</t>
+          <t>provider.support.reform@health.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Office of Parliamentary Counsel</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OPC- 2026-02</t>
+          <t>Health/E25-657123</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>stephanie.scroope@moadoph.gov.au</t>
+          <t>conference@ihacpa.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Old Parliament House</t>
+          <t>Independent Health and Aged Care Pricing Authority</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MoAD-ATM-7493</t>
+          <t>IHACPA/2526/E26-1345</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>qldtenders.pds@aurecongroup.com</t>
+          <t>aukuspillar2.industryengagement@defence.gov.au</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Defence - ISG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>S-EST11096</t>
+          <t>AUKUS PII WEB JUN 26</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>tenders@opc.gov.au</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Office of Parliamentary Counsel</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>OPC- 2026-02</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>pds.wa.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>S-EST10796</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>drisl.cfi@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>AZ6621</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>stephanie.scroope@moadoph.gov.au</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Old Parliament House</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>MoAD-ATM-7493</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
@@ -604,171 +604,171 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>saeoipreston.wdaus@jll.com</t>
+          <t>qldtenders.pds@aurecongroup.com</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>EOI PRESTON VIC</t>
+          <t>S-EST11096</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>pds.wa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Export Finance Australia</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>EFA2026002</t>
+          <t>S-EST10796</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>protocol.branch@dfat.gov.au</t>
+          <t>drisl.cfi@defence.gov.au</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>DFAT-EXD-AFS01</t>
+          <t>AZ6621</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>rcmemorial@nca.gov.au</t>
+          <t>saeoipreston.wdaus@jll.com</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>National Capital Authority</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ATM26/14</t>
+          <t>EOI PRESTON VIC</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>procurementandgrants@dewr.gov.au</t>
+          <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Export Finance Australia</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ESE24/1125-B</t>
+          <t>EFA2026002</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
+          <t>protocol.branch@dfat.gov.au</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kingscote EOI</t>
+          <t>DFAT-EXD-AFS01</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
+          <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/76225/1</t>
+          <t>ATM26/14</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>capitalprojects@questacon.edu.au</t>
+          <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ATM_2026_3289</t>
+          <t>ESE24/1125-B</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -780,83 +780,83 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>tenders@grdc.com.au</t>
+          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>PROC-9177424</t>
+          <t>Kingscote EOI</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>tenders@foodstandards.gov.au</t>
+          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Food Standards Australia New Zealand</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FSANZ-2026/6</t>
+          <t>JSD/RFT/76225/1</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>ATM_2026_3289</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+          <t>tenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>PROC-15553</t>
+          <t>PROC-9177424</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -868,17 +868,17 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>nmpb.tenders@defence.gov.au</t>
+          <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>FSANZ-2026/6</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>est10003@aurecongroup.com</t>
+          <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>DCET2026-01A</t>
+          <t>82752</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -912,17 +912,17 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>brtenders@grdc.com.au</t>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Proc-9177441</t>
+          <t>PROC-15553</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -934,77 +934,77 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+          <t>nmpb.tenders@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>80064</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>est10003@aurecongroup.com</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>DCET2026-01A</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>territories_projects@infrastructure.gov.au</t>
+          <t>brtenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>10032193</t>
+          <t>Proc-9177441</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>tenders@hsra.gov.au</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>High Speed Rail Authority</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>10031970</t>
-        </is>
-      </c>
+          <t>vt.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1014,11 +1014,19 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>tenders@ga.gov.au</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+          <t>uktnp.procurement@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Director of National Parks</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>14246</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1028,17 +1036,17 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>tenders@finance.gov.au</t>
+          <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A Testing Agency</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>DemoATM2026</t>
+          <t>10032193</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1050,17 +1058,17 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>tenders@dha.gov.au</t>
+          <t>tenders@hsra.gov.au</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Defence Housing Australia</t>
+          <t>High Speed Rail Authority</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>DHAPROC26/750</t>
+          <t>10031970</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1072,7 +1080,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
+          <t>tenders@ga.gov.au</t>
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
@@ -1086,17 +1094,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>tenders@aims.gov.au</t>
+          <t>tenders@finance.gov.au</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Australian Institute of Marine Science</t>
+          <t>A Testing Agency</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>AIMSRFT785</t>
+          <t>DemoATM2026</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1108,11 +1116,19 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>tender-pwles@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
+          <t>tenders@dha.gov.au</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Defence Housing Australia</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>DHAPROC26/750</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1122,19 +1138,11 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>statssection@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>DFAT - 26/7254-10</t>
-        </is>
-      </c>
+          <t>tenders@bom.gov.au</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1144,11 +1152,19 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ss.finance@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+          <t>tenders@aims.gov.au</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Australian Institute of Marine Science</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>AIMSRFT785</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1158,7 +1174,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
+          <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
       <c r="B34" s="3" t="n"/>
@@ -1172,17 +1188,17 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>spacecyber.events@defence.gov.au</t>
+          <t>statssection@dfat.gov.au</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>JCGSCIF26-3</t>
+          <t>DFAT - 26/7254-10</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1194,19 +1210,11 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>snsw.pds.tenders@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>S-EST11298</t>
-        </is>
-      </c>
+          <t>ss.finance@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1216,7 +1224,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
+          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
       <c r="B37" s="3" t="n"/>
@@ -1230,11 +1238,19 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>smptenders@dta.gov.au</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
+          <t>spacecyber.events@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>JCGSCIF26-3</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1244,7 +1260,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>segservicedelivery.esddewpo@defence.gov.au</t>
+          <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1254,7 +1270,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>EWPNOTICE 01/2026</t>
+          <t>S-EST11298</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1266,7 +1282,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>rfi15434@ato.gov.au</t>
+          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
@@ -1280,19 +1296,11 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>resp.priv.hospitals@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>PHS-16</t>
-        </is>
-      </c>
+          <t>smptenders@dta.gov.au</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1302,11 +1310,19 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>raiprocurement@infrastructure.gov.au</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
+          <t>segservicedelivery.esddewpo@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>EWPNOTICE 01/2026</t>
+        </is>
+      </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1316,7 +1332,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>qld.pds@bureauveritas.com</t>
+          <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="n"/>
@@ -1330,17 +1346,17 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>psprocurement@nca.gov.au</t>
+          <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>National Capital Authority</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>A26/11/1</t>
+          <t>PHS-16</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1352,7 +1368,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>procurement@rba.gov.au</t>
+          <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B45" s="3" t="n"/>
@@ -1366,7 +1382,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>procurement@npg.gov.au</t>
+          <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
       <c r="B46" s="3" t="n"/>
@@ -1380,11 +1396,19 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>procurement@moadoph.gov.au</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
+          <t>psprocurement@nca.gov.au</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>National Capital Authority</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>A26/11/1</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1394,19 +1418,11 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>procurement@harbourtrust.gov.au</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Sydney Harbour Federation Trust</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>SHFT26015</t>
-        </is>
-      </c>
+          <t>procurement@rba.gov.au</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1416,19 +1432,11 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>procurement@aciar.gov.au</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Australian Centre for International Agricultural Research</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>C005676</t>
-        </is>
-      </c>
+          <t>procurement@npg.gov.au</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1438,19 +1446,11 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>procurement.cop31@dfat.gov.au</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Department of Foreign Affairs and Trade</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>PPCOP31T-26</t>
-        </is>
-      </c>
+          <t>procurement@moadoph.gov.au</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
       <c r="D50" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1460,17 +1460,17 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>phwp.mtr@dfat.gov.au</t>
+          <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
+          <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>25A143</t>
+          <t>SHFT26015</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -1482,11 +1482,19 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>pdsvictas@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
+          <t>procurement@aciar.gov.au</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Australian Centre for International Agricultural Research</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>C005676</t>
+        </is>
+      </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1496,11 +1504,19 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>pdssa@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
+          <t>procurement.cop31@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>PPCOP31T-26</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1510,17 +1526,17 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>pds.vic.tenders@mottmac.com</t>
+          <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>S-EST10700</t>
+          <t>25A143</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1532,19 +1548,11 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>pds.sa.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>S-EST10707</t>
-        </is>
-      </c>
+          <t>pdsvictas@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
       <c r="D55" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1554,19 +1562,11 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>nbscdtender@health.gov.au</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Department of Health, Disability and Ageing</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Health/E25-515102</t>
-        </is>
-      </c>
+          <t>pdssa@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1576,17 +1576,17 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>mscspo.vlfrft@defence.gov.au</t>
+          <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/75462/1</t>
+          <t>S-EST10700</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -1598,17 +1598,17 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>mgf.contracts@dva.gov.au</t>
+          <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>MGF_17</t>
+          <t>S-EST10707</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1620,11 +1620,19 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>maugeanskateprogam@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
+          <t>nbscdtender@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Health/E25-515102</t>
+        </is>
+      </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1634,17 +1642,17 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>knowlert@ansto.gov.au</t>
+          <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Australian Nuclear Science and Technology Organisation</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>PSC002829</t>
+          <t>JSD/RFT/75462/1</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1656,17 +1664,17 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>ippreform@niaa.gov.au</t>
+          <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>PROC0018432 - NOTICE</t>
+          <t>MGF_17</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -1678,7 +1686,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>ipinfra.west@defence.gov.au</t>
+          <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B62" s="3" t="n"/>
@@ -1692,17 +1700,17 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>ests4000ph6@rpsconsulting.com</t>
+          <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>AZ6622</t>
+          <t>PSC002829</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -1714,11 +1722,19 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>entrylevelprograms@treasury.gov.au</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
+          <t>ippreform@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>National Indigenous Australians Agency</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>PROC0018432 - NOTICE</t>
+        </is>
+      </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1728,19 +1744,11 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>emily.costello@ramint.gov.au</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Royal Australian Mint</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>F26860-2</t>
-        </is>
-      </c>
+          <t>ipinfra.west@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
       <c r="D65" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1750,7 +1758,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>drisl@resources.defence.gov.au</t>
+          <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -1760,7 +1768,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>AZ6621</t>
+          <t>AZ6622</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -1772,19 +1780,11 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>dpc.invitation@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>DPC-2017</t>
-        </is>
-      </c>
+          <t>entrylevelprograms@treasury.gov.au</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
       <c r="D67" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1794,11 +1794,19 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>defence.newsmarketing@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
+          <t>emily.costello@ramint.gov.au</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Royal Australian Mint</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>F26860-2</t>
+        </is>
+      </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1808,17 +1816,17 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>def08101.acquisitions@defence.gov.au</t>
+          <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFI/88220/1</t>
+          <t>AZ6621</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -1830,11 +1838,19 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>decomdirectorate@industry.gov.au</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
+          <t>dpc.invitation@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>DPC-2017</t>
+        </is>
+      </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1844,7 +1860,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>csiroeoi2026008@csiro.au</t>
+          <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
       <c r="B71" s="3" t="n"/>
@@ -1858,11 +1874,19 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
+          <t>def08101.acquisitions@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFI/88220/1</t>
+        </is>
+      </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1872,7 +1896,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>contracts@aad.gov.au</t>
+          <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
       <c r="B73" s="3" t="n"/>
@@ -1886,7 +1910,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>contracts-enquiries@amsa.gov.au</t>
+          <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
       <c r="B74" s="3" t="n"/>
@@ -1900,7 +1924,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>commercialprojects@niaa.gov.au</t>
+          <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B75" s="3" t="n"/>
@@ -1914,19 +1938,11 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>cn.agreement@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>CNS16</t>
-        </is>
-      </c>
+          <t>contracts@aad.gov.au</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
       <c r="D76" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1936,19 +1952,11 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>cfi.trainingandevents@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>CFI-20260825</t>
-        </is>
-      </c>
+          <t>contracts-enquiries@amsa.gov.au</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
       <c r="D77" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1958,7 +1966,7 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>cei.policy@dcceew.gov.au</t>
+          <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
       <c r="B78" s="3" t="n"/>
@@ -1972,17 +1980,17 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+          <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>LSD/RFP/54755/1</t>
+          <t>CNS16</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -1994,17 +2002,17 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>bianca.james@nma.gov.au</t>
+          <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>National Museum of Australia</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>NMAT2526/14</t>
+          <t>CFI-20260825</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -2016,7 +2024,7 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>asqapanel@asqa.gov.au</t>
+          <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B81" s="3" t="n"/>
@@ -2030,11 +2038,19 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>asca.innovationchallenges@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
+          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>LSD/RFP/54755/1</t>
+        </is>
+      </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2044,17 +2060,17 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>army.industry@defence.gov.au</t>
+          <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>National Museum of Australia</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>LCD LEWG 2026</t>
+          <t>NMAT2526/14</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -2066,7 +2082,7 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>alireza.taghipour@dcceew.gov.au</t>
+          <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
       <c r="B84" s="3" t="n"/>
@@ -2080,19 +2096,11 @@
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>alexandra.torney@humanrights.gov.au</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Australian Human Rights Commission</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>National Youth OYT</t>
-        </is>
-      </c>
+          <t>asca.innovationchallenges@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n"/>
       <c r="D85" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2102,17 +2110,17 @@
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>afp-rft@afp.gov.au</t>
+          <t>army.industry@defence.gov.au</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Australian Federal Police</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>REOI 06-2026</t>
+          <t>LCD LEWG 2026</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -2124,19 +2132,11 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>aegis.training@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - CASG</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>MSCCS/RFT/77626/1</t>
-        </is>
-      </c>
+          <t>alireza.taghipour@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
       <c r="D87" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2146,17 +2146,17 @@
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>adffhp.procurement@defence.gov.au</t>
+          <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Human Rights Commission</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>ADFFHP IndustryNotic</t>
+          <t>National Youth OYT</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -2168,20 +2168,86 @@
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>afp-rft@afp.gov.au</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Australian Federal Police</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>REOI 06-2026</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>aegis.training@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>MSCCS/RFT/77626/1</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>adffhp.procurement@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>ADFFHP IndustryNotic</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (91 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (93 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,64 +494,64 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>provider.support.reform@health.gov.au</t>
+          <t>procurement@afma.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Australian Fisheries Management Authority</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Health/E25-657123</t>
+          <t>AFMA25-26-3</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>conference@ihacpa.gov.au</t>
+          <t>mim.tenders@defence.gov.au</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Independent Health and Aged Care Pricing Authority</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IHACPA/2526/E26-1345</t>
+          <t>MSD/RFQ/70006/1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>aukuspillar2.industryengagement@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Department of Defence - ISG</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>AUKUS PII WEB JUN 26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>provider.support.reform@health.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Department of Health, Disability and Ageing</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Health/E25-657123</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
@@ -560,61 +560,61 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>tenders@opc.gov.au</t>
+          <t>conference@ihacpa.gov.au</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Office of Parliamentary Counsel</t>
+          <t>Independent Health and Aged Care Pricing Authority</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>OPC- 2026-02</t>
+          <t>IHACPA/2526/E26-1345</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>stephanie.scroope@moadoph.gov.au</t>
+          <t>aukuspillar2.industryengagement@defence.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Old Parliament House</t>
+          <t>Department of Defence - ISG</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MoAD-ATM-7493</t>
+          <t>AUKUS PII WEB JUN 26</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>qldtenders.pds@aurecongroup.com</t>
+          <t>tenders@opc.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>S-EST11096</t>
+          <t>OPC- 2026-02</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -626,17 +626,17 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>pds.wa.tenders@mottmac.com</t>
+          <t>stephanie.scroope@moadoph.gov.au</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Old Parliament House</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>S-EST10796</t>
+          <t>MoAD-ATM-7493</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>drisl.cfi@defence.gov.au</t>
+          <t>qldtenders.pds@aurecongroup.com</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AZ6621</t>
+          <t>S-EST11096</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -670,149 +670,149 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>saeoipreston.wdaus@jll.com</t>
+          <t>pds.wa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>EOI PRESTON VIC</t>
+          <t>S-EST10796</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>procurement@exportfinance.gov.au</t>
+          <t>drisl.cfi@defence.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Export Finance Australia</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>EFA2026002</t>
+          <t>AZ6621</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>protocol.branch@dfat.gov.au</t>
+          <t>saeoipreston.wdaus@jll.com</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>DFAT-EXD-AFS01</t>
+          <t>EOI PRESTON VIC</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>rcmemorial@nca.gov.au</t>
+          <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>National Capital Authority</t>
+          <t>Export Finance Australia</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ATM26/14</t>
+          <t>EFA2026002</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>procurementandgrants@dewr.gov.au</t>
+          <t>protocol.branch@dfat.gov.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ESE24/1125-B</t>
+          <t>DFAT-EXD-AFS01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
+          <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Services Australia</t>
+          <t>National Capital Authority</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kingscote EOI</t>
+          <t>ATM26/14</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
+          <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/76225/1</t>
+          <t>ESE24/1125-B</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -824,17 +824,17 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>capitalprojects@questacon.edu.au</t>
+          <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Department of Industry, Science and Resources</t>
+          <t>Services Australia</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ATM_2026_3289</t>
+          <t>Kingscote EOI</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -846,61 +846,61 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>tenders@grdc.com.au</t>
+          <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Department of Defence - CASG</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>PROC-9177424</t>
+          <t>JSD/RFT/76225/1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>tenders@foodstandards.gov.au</t>
+          <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Food Standards Australia New Zealand</t>
+          <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FSANZ-2026/6</t>
+          <t>ATM_2026_3289</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>seg.groupsecurity@defence.gov.au</t>
+          <t>tenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>82752</t>
+          <t>PROC-9177424</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -912,17 +912,17 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
+          <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PROC-15553</t>
+          <t>FSANZ-2026/6</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>nmpb.tenders@defence.gov.au</t>
+          <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>82752</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -956,17 +956,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>est10003@aurecongroup.com</t>
+          <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>DCET2026-01A</t>
+          <t>PROC-15553</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -978,17 +978,17 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>brtenders@grdc.com.au</t>
+          <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Grains Research and Development Corporation</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Proc-9177441</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1000,55 +1000,55 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>vt.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+          <t>est10003@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>DCET2026-01A</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>uktnp.procurement@dcceew.gov.au</t>
+          <t>brtenders@grdc.com.au</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Director of National Parks</t>
+          <t>Grains Research and Development Corporation</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>Proc-9177441</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>territories_projects@infrastructure.gov.au</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>10032193</t>
-        </is>
-      </c>
+          <t>vt.pds@bureauveritas.com</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1058,17 +1058,17 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>tenders@hsra.gov.au</t>
+          <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>High Speed Rail Authority</t>
+          <t>Director of National Parks</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>10031970</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1080,11 +1080,19 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>tenders@ga.gov.au</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+          <t>territories_projects@infrastructure.gov.au</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>10032193</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1094,17 +1102,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>tenders@finance.gov.au</t>
+          <t>tenders@hsra.gov.au</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A Testing Agency</t>
+          <t>High Speed Rail Authority</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>DemoATM2026</t>
+          <t>10031970</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1116,19 +1124,11 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>tenders@dha.gov.au</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Defence Housing Australia</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>DHAPROC26/750</t>
-        </is>
-      </c>
+          <t>tenders@ga.gov.au</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1138,11 +1138,19 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>tenders@bom.gov.au</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
+          <t>tenders@finance.gov.au</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>A Testing Agency</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>DemoATM2026</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1152,17 +1160,17 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>tenders@aims.gov.au</t>
+          <t>tenders@dha.gov.au</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Australian Institute of Marine Science</t>
+          <t>Defence Housing Australia</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>AIMSRFT785</t>
+          <t>DHAPROC26/750</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1174,7 +1182,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>tender-pwles@dfat.gov.au</t>
+          <t>tenders@bom.gov.au</t>
         </is>
       </c>
       <c r="B34" s="3" t="n"/>
@@ -1188,17 +1196,17 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>statssection@dfat.gov.au</t>
+          <t>tenders@aims.gov.au</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Australian Institute of Marine Science</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>DFAT - 26/7254-10</t>
+          <t>AIMSRFT785</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1210,7 +1218,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ss.finance@dcceew.gov.au</t>
+          <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
@@ -1224,11 +1232,19 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
+          <t>statssection@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>DFAT - 26/7254-10</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1238,19 +1254,11 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>spacecyber.events@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>JCGSCIF26-3</t>
-        </is>
-      </c>
+          <t>ss.finance@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1260,19 +1268,11 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>snsw.pds.tenders@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>S-EST11298</t>
-        </is>
-      </c>
+          <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1282,11 +1282,19 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
+          <t>spacecyber.events@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>JCGSCIF26-3</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1296,11 +1304,19 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>smptenders@dta.gov.au</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
+          <t>snsw.pds.tenders@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>S-EST11298</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1310,19 +1326,11 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>segservicedelivery.esddewpo@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>EWPNOTICE 01/2026</t>
-        </is>
-      </c>
+          <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1332,7 +1340,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>rfi15434@ato.gov.au</t>
+          <t>smptenders@dta.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="n"/>
@@ -1346,17 +1354,17 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>resp.priv.hospitals@dva.gov.au</t>
+          <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PHS-16</t>
+          <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1368,7 +1376,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>raiprocurement@infrastructure.gov.au</t>
+          <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
       <c r="B45" s="3" t="n"/>
@@ -1382,11 +1390,19 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>qld.pds@bureauveritas.com</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
+          <t>resp.priv.hospitals@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PHS-16</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1396,19 +1412,11 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>psprocurement@nca.gov.au</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>National Capital Authority</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>A26/11/1</t>
-        </is>
-      </c>
+          <t>raiprocurement@infrastructure.gov.au</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1418,7 +1426,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>procurement@rba.gov.au</t>
+          <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
       <c r="B48" s="3" t="n"/>
@@ -1432,11 +1440,19 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>procurement@npg.gov.au</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
+          <t>psprocurement@nca.gov.au</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>National Capital Authority</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>A26/11/1</t>
+        </is>
+      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1446,7 +1462,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>procurement@moadoph.gov.au</t>
+          <t>procurement@rba.gov.au</t>
         </is>
       </c>
       <c r="B50" s="3" t="n"/>
@@ -1460,19 +1476,11 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>procurement@harbourtrust.gov.au</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Sydney Harbour Federation Trust</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>SHFT26015</t>
-        </is>
-      </c>
+          <t>procurement@npg.gov.au</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
       <c r="D51" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1482,19 +1490,11 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>procurement@aciar.gov.au</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Australian Centre for International Agricultural Research</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>C005676</t>
-        </is>
-      </c>
+          <t>procurement@moadoph.gov.au</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1504,17 +1504,17 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>procurement.cop31@dfat.gov.au</t>
+          <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>PPCOP31T-26</t>
+          <t>SHFT26015</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -1526,17 +1526,17 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>phwp.mtr@dfat.gov.au</t>
+          <t>procurement@aciar.gov.au</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
+          <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>25A143</t>
+          <t>C005676</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1548,11 +1548,19 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>pdsvictas@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
+          <t>procurement.cop31@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>PPCOP31T-26</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1562,11 +1570,19 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>pdssa@aurecongroup.com</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
+          <t>phwp.mtr@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>25A143</t>
+        </is>
+      </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1576,19 +1592,11 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>pds.vic.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>S-EST10700</t>
-        </is>
-      </c>
+          <t>pdsvictas@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
       <c r="D57" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1598,19 +1606,11 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>pds.sa.tenders@mottmac.com</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>S-EST10707</t>
-        </is>
-      </c>
+          <t>pdssa@aurecongroup.com</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
       <c r="D58" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1620,17 +1620,17 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>nbscdtender@health.gov.au</t>
+          <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Health/E25-515102</t>
+          <t>S-EST10700</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -1642,17 +1642,17 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>mscspo.vlfrft@defence.gov.au</t>
+          <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFT/75462/1</t>
+          <t>S-EST10707</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1664,17 +1664,17 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>mgf.contracts@dva.gov.au</t>
+          <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>MGF_17</t>
+          <t>Health/E25-515102</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -1686,11 +1686,19 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>maugeanskateprogam@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
+          <t>mscspo.vlfrft@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFT/75462/1</t>
+        </is>
+      </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1700,17 +1708,17 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>knowlert@ansto.gov.au</t>
+          <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Australian Nuclear Science and Technology Organisation</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>PSC002829</t>
+          <t>MGF_17</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -1722,19 +1730,11 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>ippreform@niaa.gov.au</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>National Indigenous Australians Agency</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>PROC0018432 - NOTICE</t>
-        </is>
-      </c>
+          <t>maugeanskateprogam@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
       <c r="D64" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1744,11 +1744,19 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>ipinfra.west@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
+          <t>knowlert@ansto.gov.au</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Australian Nuclear Science and Technology Organisation</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>PSC002829</t>
+        </is>
+      </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1758,17 +1766,17 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ests4000ph6@rpsconsulting.com</t>
+          <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>AZ6622</t>
+          <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -1780,7 +1788,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>entrylevelprograms@treasury.gov.au</t>
+          <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
       <c r="B67" s="3" t="n"/>
@@ -1794,17 +1802,17 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>emily.costello@ramint.gov.au</t>
+          <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Royal Australian Mint</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>F26860-2</t>
+          <t>AZ6622</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -1816,19 +1824,11 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>drisl@resources.defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>AZ6621</t>
-        </is>
-      </c>
+          <t>entrylevelprograms@treasury.gov.au</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1838,17 +1838,17 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>dpc.invitation@dva.gov.au</t>
+          <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Department of Veterans' Affairs</t>
+          <t>Royal Australian Mint</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>DPC-2017</t>
+          <t>F26860-2</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -1860,11 +1860,19 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>defence.newsmarketing@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
+          <t>drisl@resources.defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>AZ6621</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1874,17 +1882,17 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>def08101.acquisitions@defence.gov.au</t>
+          <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Veterans' Affairs</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>JSD/RFI/88220/1</t>
+          <t>DPC-2017</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -1896,7 +1904,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>decomdirectorate@industry.gov.au</t>
+          <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
       <c r="B73" s="3" t="n"/>
@@ -1910,11 +1918,19 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>csiroeoi2026008@csiro.au</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
+          <t>def08101.acquisitions@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>JSD/RFI/88220/1</t>
+        </is>
+      </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -1924,7 +1940,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>cop31procurement@dcceew.gov.au</t>
+          <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
       <c r="B75" s="3" t="n"/>
@@ -1938,7 +1954,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>contracts@aad.gov.au</t>
+          <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
       <c r="B76" s="3" t="n"/>
@@ -1952,7 +1968,7 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>contracts-enquiries@amsa.gov.au</t>
+          <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
       <c r="B77" s="3" t="n"/>
@@ -1966,7 +1982,7 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>commercialprojects@niaa.gov.au</t>
+          <t>contracts@aad.gov.au</t>
         </is>
       </c>
       <c r="B78" s="3" t="n"/>
@@ -1980,19 +1996,11 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>cn.agreement@dva.gov.au</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Department of Veterans' Affairs</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>CNS16</t>
-        </is>
-      </c>
+          <t>contracts-enquiries@amsa.gov.au</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2002,19 +2010,11 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>cfi.trainingandevents@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>CFI-20260825</t>
-        </is>
-      </c>
+          <t>commercialprojects@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n"/>
+      <c r="C80" s="3" t="n"/>
       <c r="D80" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2024,11 +2024,19 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>cei.policy@dcceew.gov.au</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
+          <t>cn.agreement@dva.gov.au</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Department of Veterans' Affairs</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>CNS16</t>
+        </is>
+      </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2038,17 +2046,17 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+          <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>LSD/RFP/54755/1</t>
+          <t>CFI-20260825</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -2060,19 +2068,11 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>bianca.james@nma.gov.au</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>National Museum of Australia</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>NMAT2526/14</t>
-        </is>
-      </c>
+          <t>cei.policy@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
       <c r="D83" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2082,11 +2082,19 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>asqapanel@asqa.gov.au</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
+          <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>LSD/RFP/54755/1</t>
+        </is>
+      </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2096,11 +2104,19 @@
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>asca.innovationchallenges@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
+          <t>bianca.james@nma.gov.au</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>National Museum of Australia</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>NMAT2526/14</t>
+        </is>
+      </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2110,19 +2126,11 @@
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>army.industry@defence.gov.au</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Department of Defence - DSRG</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>LCD LEWG 2026</t>
-        </is>
-      </c>
+          <t>asqapanel@asqa.gov.au</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n"/>
+      <c r="C86" s="3" t="n"/>
       <c r="D86" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2132,7 +2140,7 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>alireza.taghipour@dcceew.gov.au</t>
+          <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
       <c r="B87" s="3" t="n"/>
@@ -2146,17 +2154,17 @@
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>alexandra.torney@humanrights.gov.au</t>
+          <t>army.industry@defence.gov.au</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Australian Human Rights Commission</t>
+          <t>Department of Defence - DSRG</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>National Youth OYT</t>
+          <t>LCD LEWG 2026</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -2168,19 +2176,11 @@
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>afp-rft@afp.gov.au</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Australian Federal Police</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>REOI 06-2026</t>
-        </is>
-      </c>
+          <t>alireza.taghipour@dcceew.gov.au</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
       <c r="D89" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
@@ -2190,17 +2190,17 @@
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>aegis.training@defence.gov.au</t>
+          <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - CASG</t>
+          <t>Australian Human Rights Commission</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>MSCCS/RFT/77626/1</t>
+          <t>National Youth OYT</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -2212,17 +2212,17 @@
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>adffhp.procurement@defence.gov.au</t>
+          <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence - DSRG</t>
+          <t>Australian Federal Police</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>ADFFHP IndustryNotic</t>
+          <t>REOI 06-2026</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -2234,20 +2234,64 @@
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
         <is>
+          <t>aegis.training@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - CASG</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>MSCCS/RFT/77626/1</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>adffhp.procurement@defence.gov.au</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Department of Defence - DSRG</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>ADFFHP IndustryNotic</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>

--- a/tenders_email_registry.xlsx
+++ b/tenders_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,1762 +524,1762 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>provider.support.reform@health.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Health/E25-657123</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>conference@ihacpa.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Independent Health and Aged Care Pricing Authority</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>IHACPA/2526/E26-1345</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>aukuspillar2.industryengagement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - ISG</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>AUKUS PII WEB JUN 26</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tenders@opc.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Office of Parliamentary Counsel</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>OPC- 2026-02</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>stephanie.scroope@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Old Parliament House</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>MoAD-ATM-7493</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>qldtenders.pds@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>S-EST11096</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>pds.wa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>S-EST10796</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>drisl.cfi@defence.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>saeoipreston.wdaus@jll.com</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>EOI PRESTON VIC</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>procurement@exportfinance.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Export Finance Australia</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>EFA2026002</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>protocol.branch@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>DFAT-EXD-AFS01</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>rcmemorial@nca.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ATM26/14</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>procurementandgrants@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>ESE24/1125-B</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>naapt.service.delivery@servicesaustralia.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Services Australia</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Kingscote EOI</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>casgjsdlc4.lcssspocdtcommercial@defence.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/76225/1</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>capitalprojects@questacon.edu.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>ATM_2026_3289</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>tenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>PROC-9177424</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>tenders@foodstandards.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Food Standards Australia New Zealand</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>FSANZ-2026/6</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>seg.groupsecurity@defence.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>82752</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>proc-15553_talentdevelopmentprograms@ato.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>PROC-15553</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>nmpb.tenders@defence.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>80064</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>est10003@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>DCET2026-01A</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>brtenders@grdc.com.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Grains Research and Development Corporation</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Proc-9177441</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>vt.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>uktnp.procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Director of National Parks</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>14246</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>territories_projects@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>10032193</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>tenders@hsra.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>High Speed Rail Authority</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>10031970</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>tenders@ga.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>tenders@finance.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>A Testing Agency</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>DemoATM2026</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>tenders@dha.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Defence Housing Australia</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>DHAPROC26/750</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>tenders@bom.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>tenders@aims.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Australian Institute of Marine Science</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>AIMSRFT785</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>tender-pwles@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>statssection@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>DFAT - 26/7254-10</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>ss.finance@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>spc-17440_vulnerabilityspecialisttraining@ato.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>spacecyber.events@defence.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>JCGSCIF26-3</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>snsw.pds.tenders@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>S-EST11298</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>snsw-tenderinboxpds2.0@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>smptenders@dta.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>segservicedelivery.esddewpo@defence.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>EWPNOTICE 01/2026</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>rfi15434@ato.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>resp.priv.hospitals@dva.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>PHS-16</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>raiprocurement@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>qld.pds@bureauveritas.com</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>psprocurement@nca.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>National Capital Authority</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>A26/11/1</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>procurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>procurement@npg.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>procurement@moadoph.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>procurement@harbourtrust.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Sydney Harbour Federation Trust</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>SHFT26015</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>procurement@aciar.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Australian Centre for International Agricultural Research</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>C005676</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>procurement.cop31@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>PPCOP31T-26</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>phwp.mtr@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade - Australian Aid Program</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>25A143</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>pdsvictas@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>pdssa@aurecongroup.com</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>pds.vic.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>S-EST10700</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>pds.sa.tenders@mottmac.com</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>S-EST10707</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>nbscdtender@health.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Health/E25-515102</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>mscspo.vlfrft@defence.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>JSD/RFT/75462/1</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>mgf.contracts@dva.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>MGF_17</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>maugeanskateprogam@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>knowlert@ansto.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Australian Nuclear Science and Technology Organisation</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>PSC002829</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>ippreform@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>PROC0018432 - NOTICE</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>ipinfra.west@defence.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>ests4000ph6@rpsconsulting.com</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>AZ6622</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>entrylevelprograms@treasury.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>emily.costello@ramint.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Royal Australian Mint</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>F26860-2</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>drisl@resources.defence.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>AZ6621</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>dpc.invitation@dva.gov.au</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>DPC-2017</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>defence.newsmarketing@defence.gov.au</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>def08101.acquisitions@defence.gov.au</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>JSD/RFI/88220/1</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>decomdirectorate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>csiroeoi2026008@csiro.au</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>cop31procurement@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>contracts@aad.gov.au</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>contracts-enquiries@amsa.gov.au</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>commercialprojects@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>cn.agreement@dva.gov.au</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Department of Veterans' Affairs</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>CNS16</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>cfi.trainingandevents@defence.gov.au</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>CFI-20260825</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>cei.policy@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>casglsdjp8218.corporatemailbox@defence.gov.au</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>LSD/RFP/54755/1</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>bianca.james@nma.gov.au</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>National Museum of Australia</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>NMAT2526/14</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>asqapanel@asqa.gov.au</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>asca.innovationchallenges@defence.gov.au</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>army.industry@defence.gov.au</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>LCD LEWG 2026</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>alireza.taghipour@dcceew.gov.au</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>alexandra.torney@humanrights.gov.au</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Australian Human Rights Commission</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>National Youth OYT</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>afp-rft@afp.gov.au</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Australian Federal Police</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>REOI 06-2026</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>aegis.training@defence.gov.au</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - CASG</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>MSCCS/RFT/77626/1</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>adffhp.procurement@defence.gov.au</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Department of Defence - DSRG</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>ADFFHP IndustryNotic</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>65mpprocurement@rba.gov.au</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Reserve Bank of Australia</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>24/1281/44</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
